--- a/draw-design/code_nam_value.xlsx
+++ b/draw-design/code_nam_value.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="49">
   <si>
     <t>CodeCd</t>
   </si>
@@ -89,6 +89,78 @@
   </si>
   <si>
     <t>B4</t>
+  </si>
+  <si>
+    <t>HOODIE.CODE.000113</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>skill_impact_index categories</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>C5</t>
+  </si>
+  <si>
+    <t>C6</t>
+  </si>
+  <si>
+    <t>C7</t>
+  </si>
+  <si>
+    <t>C8</t>
+  </si>
+  <si>
+    <t>C9</t>
+  </si>
+  <si>
+    <t>C10</t>
+  </si>
+  <si>
+    <t>C0</t>
   </si>
 </sst>
 </file>
@@ -449,7 +521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.33203125" style="1" customWidth="1"/>
@@ -612,6 +684,193 @@
         <v>0</v>
       </c>
     </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/draw-design/code_nam_value.xlsx
+++ b/draw-design/code_nam_value.xlsx
@@ -9,12 +9,12 @@
   <sheets>
     <sheet name="CodeMaster" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="61">
   <si>
     <t>CodeCd</t>
   </si>
@@ -34,18 +34,6 @@
     <t>HOODIE.CODE.000111</t>
   </si>
   <si>
-    <t>Logic</t>
-  </si>
-  <si>
-    <t>Creative</t>
-  </si>
-  <si>
-    <t>STEM</t>
-  </si>
-  <si>
-    <t>Motor</t>
-  </si>
-  <si>
     <t>A1</t>
   </si>
   <si>
@@ -64,18 +52,6 @@
     <t>HOODIE.CODE.000112</t>
   </si>
   <si>
-    <t>0-2</t>
-  </si>
-  <si>
-    <t>3-5</t>
-  </si>
-  <si>
-    <t>6-8</t>
-  </si>
-  <si>
-    <t>9-12</t>
-  </si>
-  <si>
     <t>age_group categories</t>
   </si>
   <si>
@@ -94,9 +70,6 @@
     <t>HOODIE.CODE.000113</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>1</t>
   </si>
   <si>
@@ -157,10 +130,73 @@
     <t>C9</t>
   </si>
   <si>
-    <t>C10</t>
-  </si>
-  <si>
     <t>C0</t>
+  </si>
+  <si>
+    <t>A5</t>
+  </si>
+  <si>
+    <t>0-2 tuổi</t>
+  </si>
+  <si>
+    <t>3-5 tuổi</t>
+  </si>
+  <si>
+    <t>6-8 tuổi</t>
+  </si>
+  <si>
+    <t>9-12 tuổi</t>
+  </si>
+  <si>
+    <t>B5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lớn hơn13 tuổi </t>
+  </si>
+  <si>
+    <t>Tư duy (Logic)</t>
+  </si>
+  <si>
+    <t>Sáng tạo (Creative)</t>
+  </si>
+  <si>
+    <t>Stem (STEM)</t>
+  </si>
+  <si>
+    <t>Vận động (Motor)</t>
+  </si>
+  <si>
+    <t>Xã hội (Social)</t>
+  </si>
+  <si>
+    <t>HOODIE.CODE.000114</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>difficulty_level</t>
+  </si>
+  <si>
+    <t>Người mới bắt đầu</t>
+  </si>
+  <si>
+    <t>Trung cấp</t>
+  </si>
+  <si>
+    <t>Trình độ cao</t>
+  </si>
+  <si>
+    <t>Chuyên gia</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>D4</t>
   </si>
 </sst>
 </file>
@@ -184,7 +220,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -194,6 +230,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -210,13 +252,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -521,7 +564,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.33203125" style="1" customWidth="1"/>
@@ -529,9 +572,10 @@
     <col min="3" max="3" width="20.5546875" customWidth="1"/>
     <col min="4" max="4" width="23.6640625" customWidth="1"/>
     <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -548,327 +592,508 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
       <c r="E2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G2" t="str">
+        <f>"INSERT INTO code_master (code_cd, code_name, code_value, code_description, delete_flag) VALUES ('" &amp; A2 &amp; "', '" &amp; B2 &amp; "', '" &amp; C2 &amp; "', '" &amp; D2 &amp; "', " &amp; E2 &amp; ");"</f>
+        <v>INSERT INTO code_master (code_cd, code_name, code_value, code_description, delete_flag) VALUES ('HOODIE.CODE.000111', 'A1', 'Tư duy (Logic)', 'skill_type categories', 0);</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G3" t="str">
+        <f t="shared" ref="G3:G25" si="0">"INSERT INTO code_master (code_cd, code_name, code_value, code_description, delete_flag) VALUES ('" &amp; A3 &amp; "', '" &amp; B3 &amp; "', '" &amp; C3 &amp; "', '" &amp; D3 &amp; "', " &amp; E3 &amp; ");"</f>
+        <v>INSERT INTO code_master (code_cd, code_name, code_value, code_description, delete_flag) VALUES ('HOODIE.CODE.000111', 'A2', 'Sáng tạo (Creative)', 'skill_type categories', 0);</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G4" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO code_master (code_cd, code_name, code_value, code_description, delete_flag) VALUES ('HOODIE.CODE.000111', 'A3', 'Stem (STEM)', 'skill_type categories', 0);</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="G5" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO code_master (code_cd, code_name, code_value, code_description, delete_flag) VALUES ('HOODIE.CODE.000111', 'A4', 'Vận động (Motor)', 'skill_type categories', 0);</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="G6" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO code_master (code_cd, code_name, code_value, code_description, delete_flag) VALUES ('HOODIE.CODE.000111', 'A5', 'Xã hội (Social)', 'skill_type categories', 0);</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="C7" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="G7" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO code_master (code_cd, code_name, code_value, code_description, delete_flag) VALUES ('HOODIE.CODE.000112', 'B1', '0-2 tuổi', 'age_group categories', 0);</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="C8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="G8" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO code_master (code_cd, code_name, code_value, code_description, delete_flag) VALUES ('HOODIE.CODE.000112', 'B2', '3-5 tuổi', 'age_group categories', 0);</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C9" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="G9" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO code_master (code_cd, code_name, code_value, code_description, delete_flag) VALUES ('HOODIE.CODE.000112', 'B3', '6-8 tuổi', 'age_group categories', 0);</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="G10" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO code_master (code_cd, code_name, code_value, code_description, delete_flag) VALUES ('HOODIE.CODE.000112', 'B4', '9-12 tuổi', 'age_group categories', 0);</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="G11" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO code_master (code_cd, code_name, code_value, code_description, delete_flag) VALUES ('HOODIE.CODE.000112', 'B5', 'lớn hơn13 tuổi ', 'age_group categories', 0);</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="G12" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO code_master (code_cd, code_name, code_value, code_description, delete_flag) VALUES ('HOODIE.CODE.000113', 'C0', '1', 'skill_impact_index categories', 0);</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="G13" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO code_master (code_cd, code_name, code_value, code_description, delete_flag) VALUES ('HOODIE.CODE.000113', 'C1', '2', 'skill_impact_index categories', 0);</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="G14" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO code_master (code_cd, code_name, code_value, code_description, delete_flag) VALUES ('HOODIE.CODE.000113', 'C2', '3', 'skill_impact_index categories', 0);</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="D15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="G15" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO code_master (code_cd, code_name, code_value, code_description, delete_flag) VALUES ('HOODIE.CODE.000113', 'C3', '4', 'skill_impact_index categories', 0);</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D16" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="G16" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO code_master (code_cd, code_name, code_value, code_description, delete_flag) VALUES ('HOODIE.CODE.000113', 'C4', '5', 'skill_impact_index categories', 0);</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
+      <c r="B17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="1" t="s">
+      <c r="D17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="G17" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO code_master (code_cd, code_name, code_value, code_description, delete_flag) VALUES ('HOODIE.CODE.000113', 'C5', '6', 'skill_impact_index categories', 0);</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="D18" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="G18" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO code_master (code_cd, code_name, code_value, code_description, delete_flag) VALUES ('HOODIE.CODE.000113', 'C6', '7', 'skill_impact_index categories', 0);</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" s="5" t="s">
+      <c r="D19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="G19" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO code_master (code_cd, code_name, code_value, code_description, delete_flag) VALUES ('HOODIE.CODE.000113', 'C7', '8', 'skill_impact_index categories', 0);</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D20" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="G20" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO code_master (code_cd, code_name, code_value, code_description, delete_flag) VALUES ('HOODIE.CODE.000113', 'C8', '9', 'skill_impact_index categories', 0);</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="5" t="s">
+      <c r="C21" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="5" t="s">
+      <c r="D21" t="s">
         <v>28</v>
       </c>
-      <c r="D12" t="s">
-        <v>37</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" t="s">
-        <v>37</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" t="s">
-        <v>37</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" t="s">
-        <v>37</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D17" t="s">
-        <v>37</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D19" t="s">
-        <v>37</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D20" t="s">
-        <v>37</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="G21" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO code_master (code_cd, code_name, code_value, code_description, delete_flag) VALUES ('HOODIE.CODE.000113', 'C9', '10', 'skill_impact_index categories', 0);</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" t="s">
+        <v>53</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="G22" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO code_master (code_cd, code_name, code_value, code_description, delete_flag) VALUES ('HOODIE.CODE.000114', 'D1', 'Người mới bắt đầu', 'difficulty_level', 0);</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" t="s">
+        <v>53</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="G23" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO code_master (code_cd, code_name, code_value, code_description, delete_flag) VALUES ('HOODIE.CODE.000114', 'D2', 'Trung cấp', 'difficulty_level', 0);</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" t="s">
+        <v>53</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="G24" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO code_master (code_cd, code_name, code_value, code_description, delete_flag) VALUES ('HOODIE.CODE.000114', 'D3', 'Trình độ cao', 'difficulty_level', 0);</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25" t="s">
+        <v>53</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="G25" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO code_master (code_cd, code_name, code_value, code_description, delete_flag) VALUES ('HOODIE.CODE.000114', 'D4', 'Chuyên gia', 'difficulty_level', 0);</v>
       </c>
     </row>
   </sheetData>

--- a/draw-design/code_nam_value.xlsx
+++ b/draw-design/code_nam_value.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="69">
   <si>
     <t>CodeCd</t>
   </si>
@@ -197,6 +197,30 @@
   </si>
   <si>
     <t>D4</t>
+  </si>
+  <si>
+    <t>HOODIE.CODE.000115</t>
+  </si>
+  <si>
+    <t>GENDER1</t>
+  </si>
+  <si>
+    <t>GENDER2</t>
+  </si>
+  <si>
+    <t>GENDER3</t>
+  </si>
+  <si>
+    <t>Nam</t>
+  </si>
+  <si>
+    <t>Nữ</t>
+  </si>
+  <si>
+    <t>Khác</t>
+  </si>
+  <si>
+    <t>gender</t>
   </si>
 </sst>
 </file>
@@ -564,7 +588,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.33203125" style="1" customWidth="1"/>
@@ -630,7 +654,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="str">
-        <f t="shared" ref="G3:G25" si="0">"INSERT INTO code_master (code_cd, code_name, code_value, code_description, delete_flag) VALUES ('" &amp; A3 &amp; "', '" &amp; B3 &amp; "', '" &amp; C3 &amp; "', '" &amp; D3 &amp; "', " &amp; E3 &amp; ");"</f>
+        <f t="shared" ref="G3:G28" si="0">"INSERT INTO code_master (code_cd, code_name, code_value, code_description, delete_flag) VALUES ('" &amp; A3 &amp; "', '" &amp; B3 &amp; "', '" &amp; C3 &amp; "', '" &amp; D3 &amp; "', " &amp; E3 &amp; ");"</f>
         <v>INSERT INTO code_master (code_cd, code_name, code_value, code_description, delete_flag) VALUES ('HOODIE.CODE.000111', 'A2', 'Sáng tạo (Creative)', 'skill_type categories', 0);</v>
       </c>
     </row>
@@ -1094,6 +1118,69 @@
       <c r="G25" t="str">
         <f t="shared" si="0"/>
         <v>INSERT INTO code_master (code_cd, code_name, code_value, code_description, delete_flag) VALUES ('HOODIE.CODE.000114', 'D4', 'Chuyên gia', 'difficulty_level', 0);</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26" t="s">
+        <v>68</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="G26" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO code_master (code_cd, code_name, code_value, code_description, delete_flag) VALUES ('HOODIE.CODE.000115', 'GENDER1', 'Nam', 'gender', 0);</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" t="s">
+        <v>68</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="G27" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO code_master (code_cd, code_name, code_value, code_description, delete_flag) VALUES ('HOODIE.CODE.000115', 'GENDER2', 'Nữ', 'gender', 0);</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C28" t="s">
+        <v>67</v>
+      </c>
+      <c r="D28" t="s">
+        <v>68</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="G28" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO code_master (code_cd, code_name, code_value, code_description, delete_flag) VALUES ('HOODIE.CODE.000115', 'GENDER3', 'Khác', 'gender', 0);</v>
       </c>
     </row>
   </sheetData>
